--- a/ktds/AI/AI_커리큘럼_KTDS.xlsx
+++ b/ktds/AI/AI_커리큘럼_KTDS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dreamondal/Documents/제안/KTDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B860828C-BDE0-E14E-BD96-63A7CF05A8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31492D1-2337-FB4C-A49A-80D3B933CCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AI 교육 커리큘럼" sheetId="1" r:id="rId1"/>
+    <sheet name="AI 교육 커리큘럼" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'AI 교육 커리큘럼'!$4:$4</definedName>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>교육 목표</t>
   </si>
@@ -65,31 +65,6 @@
   </si>
   <si>
     <t>1H</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>2H</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>2일, 14시간</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAS 이해</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[실습]
-질문에 따라 코드 생성 또는 Q&amp;A를 수행하는 에이젼트 개발 
-- 질문 분류: Code 생성 요청 또는 Q&amp;A 
-- Code 생성 요청 시 
-  - 코드 벡터DB 검색 -&gt; 코드 생성 -&gt; 결과 평가 
-  - 결과 평가 점수가 낮으면 재시도 
-- Q&amp;A   
-  - 내부벡터DB 검색 +, 외부정보(웹 + YouTube) 검색  
-  - 결과 평가 점수가 낮으면 재시도 
-- 재시도 횟수 초과 시 Fallback 처리 </t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -116,63 +91,157 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>업무 자동화 플러그인 개발</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">■ DMAP 플러그인 이해 
-- DMAP 플러그인 개요: 코딩 없이 플러그인 개발을 지원하는 플러그인 
-- 스킬, 에이젼트 구성 이해 
-- 설치 및 사용법 이해 </t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[실습] 
-- 특정 주제에 대해 웹+유튜브 검색하여 레포트 작성하는 플러그인 개발 및 플러그인 기능 확장 
-- 개인별 주제를 선정하여 플러그인 개발 </t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>4H</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>업무자동화 MAS 개발</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1일차</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>2일차</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>■ MAS 기본 이해
-- 정의, 필요성 
-- 구축방안: SAS패턴 적용, 외부 툴/시스템과의 통신 방식, 상태 관리 
-- 하네스 엔지니어링: 비용, 성능, 보안 관점 
-- LangGraph 이해</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>멀티에이전트 시스템을 이용한 업무 자동화 역량 향상</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>업무자동화에 AI를 이용하고 싶은 모든 직원</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">■ Abra 플러그인 이해 
-- Abra 플러그인 개요: Dify로 워크플로우를 설계하여 LangGraph로 MAS구축  
-- 스킬, 에이젼트 구성 이해 
-- 설치 및 사용법 이해 </t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t xml:space="preserve">■ AI 개요
+ - 3대 필요성과 5대 핵심 구성요소
+ - AI 어플리케이션 아키텍처와 개발 흐름
+■ AI 도구 지형과 트렌드 
+- Layer1: Foundation Model 
+- Layer2: AI 코딩툴 
+- Layer3: Workflow 빌더 
+- Layer4: Agentic AI 개발 프레임워크 
+- Layer5: 클라우드 AI PaaS </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agentic AI 실행 환경 설계 및 멀티에이전트 시스템 개발 역량 확보 (엔터프라이즈 AI 활용 포함)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2일, 16시간</t>
+  </si>
+  <si>
+    <t>IT 개발자 (AI 서비스 개발자, 백엔드/풀스택 개발자)</t>
+  </si>
+  <si>
+    <t>Python 기초
+문법</t>
+  </si>
+  <si>
+    <t>1회차
+(8H)</t>
   </si>
   <si>
     <t xml:space="preserve">[실습]
+• 개발 환경 구성: Claude Code, vscode, docker, dify 
+</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5H</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agentic AI 구조와
+핵심 패턴</t>
+  </si>
+  <si>
+    <t>■ LangChain 이해
+ - 5대 핵심 구성별 이해: Workflow, LLM인터페이스,
+   RAG, Tools, State관리
+■ MAS 아키텍처
+ - SAS(Schedule-Agent-Supervisor) 패턴
+ - 상태관리 기법, MAS 내/외부 통신 방법
+■ Function Calling과 Tool Use
+ - 공통 5단계 워크플로우
+ - OpenAI / Claude / Gemini 3사 비교
+ - 병렬/순차 호출 &amp; 스트리밍</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[실습]
+• Function Calling 실습: Travel Planner
+- 날씨, 관광지, 음식점을 검색하여 여행 장소 부근의 오늘의 여행 루트 추천 </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.5H</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG / GraphRAG 개요</t>
+  </si>
+  <si>
+    <t>■ RAG(Retrieval-Augmented Generation) 기초
+ - RAG 필요성과 아키텍처 &amp; 검색 기법
+ - 인덱싱: Load → Split → Embed → Store
+ - 검색 메커니즘: 시맨틱 검색, 하이브리드 검색
+■ RAG 품질 튜닝
+ - 인덱싱: 청킹전략, 임베딩 최적화, 벡터스토어 파라미터 튜닝
+ - 검색: 쿼리 최적화, 하이브리드 검색 전략, 리랭킹
+ - 평가 및 메트릭
+■ GraphRAG
+ - Vector RAG vs GraphRAG 비교
+ - 멀티홉 추론, Knowledge Graph 구축
+ - LightRAG / Neo4j 이해</t>
+  </si>
+  <si>
+    <t>[실습 및 데모]
+• 기본 RAG 시스템 구축 실습
+  (Chroma + Multi-Query Retriever)
+• RAG 품질 평가(RAGAS) 데모
+• GraphRAG 구축 데모 관찰</t>
+  </si>
+  <si>
+    <t>2회차
+(8H)</t>
+  </si>
+  <si>
+    <t>MCP 개발</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>■ MCP(Model Context Protocol)
+ - Host-Client-Server 아키텍처
+ - 프로토콜: JSON-RPC 2.0, 전송방식(Stdio/HTTP)
+ - 기본 기능: Tools, Resources, Prompts Primitives
+ - 고급 기능: Sampling, Elicitation, 인증/인가(OAuth 2.1)
+■ MCP 서버 커스텀 구현
+ - 커스텀 Tool 개발, 외부 API 연동
+ - MCP SDK 활용 (Python/TypeScript)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[실습]
+• MCP 서버 구현 및 Claude 연동 실습</t>
+  </si>
+  <si>
+    <t>2H</t>
+  </si>
+  <si>
+    <t>LangGraph &amp; MAS
+통합 개발</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>■ 멀티에이젼트 아키텍처
+ - Agent 정의: LLM + 외부 호출 + Loop
+ - 단일 에이전트 vs 멀티에이젼트 비교
+ - SAS 패턴 (Scheduler-Agent-Supervisor)
+   · Scheduler: Agent Card 분석, 작업 분해, 실행 순서 결정
+   · Agent: 전문 영역 작업 처리, 결과 반환
+   · Supervisor: 진행 추적, 이상 감지, 품질 평가, 종료/재시도 판단
+ - 통신 구조: 수평적(Agent 간) / 수직적(Agent→외부)
+ - 프로토콜 선택: Function Calling / MCP / API
+■ 아키텍처 패턴 (SAS의 변형)
+ - ReAct: 추론(Thought) → 행동(Action) → 관찰(Observation) 반복
+ - Planning &amp; Execution: 계획 수립 후 단계별 실행
+ - Multi-Agent Collaboration: 전문 에이전트 간 협업
+■ 상태 관리 (State Management)
+ - 상태의 종류: 단기(Context Window) / 장기(DB) / 작업(Shared State)
+ - Checkpointing: 장애 복구를 위한 단계별 상태 저장
+ - Shared State Pattern: Redis/PostgreSQL 기반 에이전트 간 정보 공유
+ - Persistence: 시스템 재시작 후 대화 맥락 유지
+■ 운영 안정성 (Operational Safety)
+ - 주요 리스크: 무한 Loop, 토큰 누수, 에이전트 폭주, 할루시네이션 전파
+ - Loop 종료 조건: 최대 반복 횟수, 타임아웃, 비용 한도, 품질 임계값
+ - Agent 호출 예산(Budget): 토큰/비용/호출/시간 예산 할당
+ - Supervisor Kill-switch: Budget 초과, 무한 Loop, 연속 실패 시 강제 종료
+ - Human-in-the-Loop(HITL): 고비용·비가역적·불확실 작업 시 승인 워크플로우
+ - 운영 모니터링: 비용, 지연, 실패율, 토큰, Loop 횟수, HITL 거부율</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[실습]
 ■ 실습 서비스: KT 채널 활용 AI 소상공인 마케팅 지원 서비스
  1) 업종/지역/시즌 트렌드 분석
  2) 예산별 온/오프라인 이벤트 생성
@@ -183,37 +252,61 @@
   - 비즈니스 요구사항을 프롬프트로 전환하는 방법 체험
   - AI가 생성한 시나리오 검토 및 선택
  [설계] Dify DSL 자동생성 → Dify 프로토타이핑
-  - DSL 수정 → 재검증 → 재시도 루프 
+  - DSL 수정 → 재검증 → 재시도 루프 관찰 및 이해
   - Visual Builder(Dify)에서 워크플로우 동작 확인
  [개발] 개발계획서 → RAG → MAS 개발 → 프론트엔드 연동
-  - LangChain + LangGraph 기반 MAS 구축 
+  - LangChain + LangGraph 기반 MAS 구축 과정 관찰
   - 프롬프트만으로 실제 업무 결과물 산출 체험
  [배포] Docker Compose로 컨테이너 이미지 생성 및 로컬 배포
+  - (VM 준비 시 서버 배포)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.5H</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Claude 플러그인
+동작 원리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ Claude Code 플러그인 구성요소 이해
+ - Commands, Skills, Agents의 역할과 관계
+ - 선언적 방식의 플러그인 사용 방법 이해
 </t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">■ AI 개요
- - 3대 필요성과 5대 핵심 구성요소
- - AI 어플리케이션 아키텍처와 개발 흐름
-■ AI 도구 지형과 트렌드 
-- Layer1: Foundation Model 
-- Layer2: AI 코딩툴 
-- Layer3: Workflow 빌더 
-- Layer4: Agentic AI 개발 프레임워크 
-- Layer5: 클라우드 AI PaaS </t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI 기초</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t xml:space="preserve">[실습]
+- blog poster 개발 
+  - 주제 키워드 입력 
+  - 웹검색, 기술문서 조사, 트렌드 분석 
+  - SEO 최적화 , AI 이미지 생성 
+  - 최종 Word 문서 생성 
+</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wrap-up</t>
+  </si>
+  <si>
+    <t>■ 2일간 학습 내용 정리
+■ Lessons &amp; Learned 공유</t>
+  </si>
+  <si>
+    <t>[토론]
+• Lessons &amp; Learned 공유</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5H</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +367,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -298,7 +398,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -338,50 +438,100 @@
       <top style="thin">
         <color rgb="FF999999"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{A86BDF09-A4D0-264D-9340-35D3BA46C031}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -680,160 +830,208 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1740E0-5585-B142-B237-DB857F70B880}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="58" customWidth="1"/>
-    <col min="4" max="4" width="45.1640625" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="1" max="1" width="8" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22" style="5" customWidth="1"/>
+    <col min="3" max="3" width="58" style="5" customWidth="1"/>
+    <col min="4" max="4" width="45.1640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="9"/>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>14</v>
+      <c r="E1" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="35" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="9"/>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="22" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="150">
+      <c r="A5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="120">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="181" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="206" customHeight="1">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="152.5" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="20" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="4" spans="1:5" ht="22" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="150" customHeight="1">
-      <c r="A5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6" t="s">
+      <c r="D9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="409.5" customHeight="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="123.5" customHeight="1">
+      <c r="A11" s="16"/>
+      <c r="B11" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="131" customHeight="1">
-      <c r="A6" s="11"/>
-      <c r="B6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="86" customHeight="1">
-      <c r="A7" s="11"/>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="152.5" customHeight="1">
-      <c r="A8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="326" customHeight="1">
-      <c r="A9" s="11"/>
-      <c r="B9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>23</v>
+    <row r="12" spans="1:5" ht="42" customHeight="1">
+      <c r="A12" s="16"/>
+      <c r="B12" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B1:C1"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
